--- a/site/public/downloads/ken/ken-seniors.xlsx
+++ b/site/public/downloads/ken/ken-seniors.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>台灣個人／家庭通膨每年 10% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 10% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 10% 會被拒絕，公式也以 MAX(10%, 輸入值) 計算。</t>
+          <t>台灣個人／家庭通膨每年 5% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 5% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 5% 會被拒絕，公式也以 MAX(5%, 輸入值) 計算。</t>
         </is>
       </c>
     </row>
@@ -770,15 +770,15 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>$B$7/SUMPRODUCT(((1+MAX(0.1,$B$9))/(1+$B$8))^(ROW(INDIRECT("1:"&amp;MAX(1,$B$5-$B$4)))-1))</f>
+        <f>$B$7/SUMPRODUCT(((1+MAX(0.05,$B$9))/(1+$B$8))^(ROW(INDIRECT("1:"&amp;MAX(1,$B$5-$B$4)))-1))</f>
         <v/>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
         <v/>
       </c>
       <c r="B30" s="19">
-        <f>B29*(1+MAX(0.1,$B$9))</f>
+        <f>B29*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C30" s="19">
@@ -1054,7 +1054,7 @@
         <v/>
       </c>
       <c r="B31" s="19">
-        <f>B30*(1+MAX(0.1,$B$9))</f>
+        <f>B30*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C31" s="19">
@@ -1080,7 +1080,7 @@
         <v/>
       </c>
       <c r="B32" s="19">
-        <f>B31*(1+MAX(0.1,$B$9))</f>
+        <f>B31*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C32" s="19">
@@ -1106,7 +1106,7 @@
         <v/>
       </c>
       <c r="B33" s="19">
-        <f>B32*(1+MAX(0.1,$B$9))</f>
+        <f>B32*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C33" s="19">
@@ -1132,7 +1132,7 @@
         <v/>
       </c>
       <c r="B34" s="19">
-        <f>B33*(1+MAX(0.1,$B$9))</f>
+        <f>B33*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C34" s="19">
@@ -1158,7 +1158,7 @@
         <v/>
       </c>
       <c r="B35" s="19">
-        <f>B34*(1+MAX(0.1,$B$9))</f>
+        <f>B34*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C35" s="19">
@@ -1184,7 +1184,7 @@
         <v/>
       </c>
       <c r="B36" s="19">
-        <f>B35*(1+MAX(0.1,$B$9))</f>
+        <f>B35*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C36" s="19">
@@ -1210,7 +1210,7 @@
         <v/>
       </c>
       <c r="B37" s="19">
-        <f>B36*(1+MAX(0.1,$B$9))</f>
+        <f>B36*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C37" s="19">
@@ -1236,7 +1236,7 @@
         <v/>
       </c>
       <c r="B38" s="19">
-        <f>B37*(1+MAX(0.1,$B$9))</f>
+        <f>B37*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C38" s="19">
@@ -1262,7 +1262,7 @@
         <v/>
       </c>
       <c r="B39" s="19">
-        <f>B38*(1+MAX(0.1,$B$9))</f>
+        <f>B38*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C39" s="19">
@@ -1288,7 +1288,7 @@
         <v/>
       </c>
       <c r="B40" s="19">
-        <f>B39*(1+MAX(0.1,$B$9))</f>
+        <f>B39*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C40" s="19">
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="B41" s="19">
-        <f>B40*(1+MAX(0.1,$B$9))</f>
+        <f>B40*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C41" s="19">
@@ -1340,7 +1340,7 @@
         <v/>
       </c>
       <c r="B42" s="19">
-        <f>B41*(1+MAX(0.1,$B$9))</f>
+        <f>B41*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C42" s="19">
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="B43" s="19">
-        <f>B42*(1+MAX(0.1,$B$9))</f>
+        <f>B42*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C43" s="19">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="B44" s="19">
-        <f>B43*(1+MAX(0.1,$B$9))</f>
+        <f>B43*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C44" s="19">
@@ -1418,7 +1418,7 @@
         <v/>
       </c>
       <c r="B45" s="19">
-        <f>B44*(1+MAX(0.1,$B$9))</f>
+        <f>B44*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C45" s="19">
@@ -1444,7 +1444,7 @@
         <v/>
       </c>
       <c r="B46" s="19">
-        <f>B45*(1+MAX(0.1,$B$9))</f>
+        <f>B45*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C46" s="19">
@@ -1470,7 +1470,7 @@
         <v/>
       </c>
       <c r="B47" s="19">
-        <f>B46*(1+MAX(0.1,$B$9))</f>
+        <f>B46*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C47" s="19">
@@ -1496,7 +1496,7 @@
         <v/>
       </c>
       <c r="B48" s="19">
-        <f>B47*(1+MAX(0.1,$B$9))</f>
+        <f>B47*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C48" s="19">
@@ -1522,7 +1522,7 @@
         <v/>
       </c>
       <c r="B49" s="19">
-        <f>B48*(1+MAX(0.1,$B$9))</f>
+        <f>B48*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C49" s="19">
@@ -1548,7 +1548,7 @@
         <v/>
       </c>
       <c r="B50" s="19">
-        <f>B49*(1+MAX(0.1,$B$9))</f>
+        <f>B49*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C50" s="19">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="B51" s="19">
-        <f>B50*(1+MAX(0.1,$B$9))</f>
+        <f>B50*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C51" s="19">
@@ -1600,7 +1600,7 @@
         <v/>
       </c>
       <c r="B52" s="19">
-        <f>B51*(1+MAX(0.1,$B$9))</f>
+        <f>B51*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C52" s="19">
@@ -1626,7 +1626,7 @@
         <v/>
       </c>
       <c r="B53" s="19">
-        <f>B52*(1+MAX(0.1,$B$9))</f>
+        <f>B52*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C53" s="19">
@@ -1652,7 +1652,7 @@
         <v/>
       </c>
       <c r="B54" s="19">
-        <f>B53*(1+MAX(0.1,$B$9))</f>
+        <f>B53*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C54" s="19">
@@ -1678,7 +1678,7 @@
         <v/>
       </c>
       <c r="B55" s="19">
-        <f>B54*(1+MAX(0.1,$B$9))</f>
+        <f>B54*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C55" s="19">
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="B56" s="19">
-        <f>B55*(1+MAX(0.1,$B$9))</f>
+        <f>B55*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C56" s="19">
@@ -1730,7 +1730,7 @@
         <v/>
       </c>
       <c r="B57" s="19">
-        <f>B56*(1+MAX(0.1,$B$9))</f>
+        <f>B56*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C57" s="19">
@@ -1756,7 +1756,7 @@
         <v/>
       </c>
       <c r="B58" s="19">
-        <f>B57*(1+MAX(0.1,$B$9))</f>
+        <f>B57*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C58" s="19">
@@ -1782,7 +1782,7 @@
         <v/>
       </c>
       <c r="B59" s="19">
-        <f>B58*(1+MAX(0.1,$B$9))</f>
+        <f>B58*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C59" s="19">
@@ -1808,7 +1808,7 @@
         <v/>
       </c>
       <c r="B60" s="19">
-        <f>B59*(1+MAX(0.1,$B$9))</f>
+        <f>B59*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C60" s="19">
@@ -1834,7 +1834,7 @@
         <v/>
       </c>
       <c r="B61" s="19">
-        <f>B60*(1+MAX(0.1,$B$9))</f>
+        <f>B60*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C61" s="19">
@@ -1860,7 +1860,7 @@
         <v/>
       </c>
       <c r="B62" s="19">
-        <f>B61*(1+MAX(0.1,$B$9))</f>
+        <f>B61*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C62" s="19">
@@ -1886,7 +1886,7 @@
         <v/>
       </c>
       <c r="B63" s="19">
-        <f>B62*(1+MAX(0.1,$B$9))</f>
+        <f>B62*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C63" s="19">
@@ -1912,7 +1912,7 @@
         <v/>
       </c>
       <c r="B64" s="19">
-        <f>B63*(1+MAX(0.1,$B$9))</f>
+        <f>B63*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C64" s="19">
@@ -1938,7 +1938,7 @@
         <v/>
       </c>
       <c r="B65" s="19">
-        <f>B64*(1+MAX(0.1,$B$9))</f>
+        <f>B64*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C65" s="19">
@@ -1964,7 +1964,7 @@
         <v/>
       </c>
       <c r="B66" s="19">
-        <f>B65*(1+MAX(0.1,$B$9))</f>
+        <f>B65*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C66" s="19">
@@ -1990,7 +1990,7 @@
         <v/>
       </c>
       <c r="B67" s="19">
-        <f>B66*(1+MAX(0.1,$B$9))</f>
+        <f>B66*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C67" s="19">
@@ -2016,7 +2016,7 @@
         <v/>
       </c>
       <c r="B68" s="19">
-        <f>B67*(1+MAX(0.1,$B$9))</f>
+        <f>B67*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C68" s="19">
@@ -2042,7 +2042,7 @@
         <v/>
       </c>
       <c r="B69" s="19">
-        <f>B68*(1+MAX(0.1,$B$9))</f>
+        <f>B68*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C69" s="19">
@@ -2068,7 +2068,7 @@
         <v/>
       </c>
       <c r="B70" s="19">
-        <f>B69*(1+MAX(0.1,$B$9))</f>
+        <f>B69*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C70" s="19">
@@ -2094,7 +2094,7 @@
         <v/>
       </c>
       <c r="B71" s="19">
-        <f>B70*(1+MAX(0.1,$B$9))</f>
+        <f>B70*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C71" s="19">
@@ -2120,7 +2120,7 @@
         <v/>
       </c>
       <c r="B72" s="19">
-        <f>B71*(1+MAX(0.1,$B$9))</f>
+        <f>B71*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C72" s="19">
@@ -2146,7 +2146,7 @@
         <v/>
       </c>
       <c r="B73" s="19">
-        <f>B72*(1+MAX(0.1,$B$9))</f>
+        <f>B72*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C73" s="19">
@@ -2172,7 +2172,7 @@
         <v/>
       </c>
       <c r="B74" s="19">
-        <f>B73*(1+MAX(0.1,$B$9))</f>
+        <f>B73*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
       <c r="C74" s="19">
@@ -2205,8 +2205,8 @@
     <mergeCell ref="A75:F75"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2315,15 +2315,15 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="B20" s="15">
-        <f>($B$6+$B$7)*(1+MAX(0.1,$B$10))^$B$4</f>
+        <f>($B$6+$B$7)*(1+MAX(0.05,$B$10))^$B$4</f>
         <v/>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>($B$6+$B$7)*(1+MAX(0.1,$B$10))^$B$4*((1+MAX(0.1,$B$10))^(ROUND($B$5*12,0)/12)-1)/((1+MAX(0.1,$B$10))^(1/12)-1)</f>
+        <f>($B$6+$B$7)*(1+MAX(0.05,$B$10))^$B$4*((1+MAX(0.05,$B$10))^(ROUND($B$5*12,0)/12)-1)/((1+MAX(0.05,$B$10))^(1/12)-1)</f>
         <v/>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="B22" s="15">
-        <f>($B$8+$B$9)*(1+MAX(0.1,$B$10))^$B$4</f>
+        <f>($B$8+$B$9)*(1+MAX(0.05,$B$10))^$B$4</f>
         <v/>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="B24" s="15">
-        <f>$B$23/(1+MAX(0.1,$B$10))^$B$4</f>
+        <f>$B$23/(1+MAX(0.05,$B$10))^$B$4</f>
         <v/>
       </c>
     </row>
@@ -2493,8 +2493,8 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3152,15 +3152,15 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="B12" s="15">
-        <f>SUM(B6:B8)*(1+MAX(0.1,$B$9))</f>
+        <f>SUM(B6:B8)*(1+MAX(0.05,$B$9))</f>
         <v/>
       </c>
     </row>
@@ -3776,8 +3776,8 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
     <dataValidation sqref="B15:B98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"日常基本開銷,醫療保健,休閒娛樂"</formula1>
